--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 03/XKSX_VoHopLE-UPG_160326.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 03/XKSX_VoHopLE-UPG_160326.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42930AC-694C-487A-A30C-0493A506B66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A17BD3-4973-418B-BDB7-928957B95E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XuatKho_SX" sheetId="10" r:id="rId1"/>
+    <sheet name="DS_DaiLy" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DS_DaiLy!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
   <si>
     <t>STT</t>
   </si>
@@ -114,6 +116,69 @@
   </si>
   <si>
     <t>Sản xuất LE-2G nâng cấp LE-4G</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>Minh Huy</t>
+  </si>
+  <si>
+    <t>ĐL Ngọc Kim Anh (Ngọc Hoàn)</t>
+  </si>
+  <si>
+    <t>ĐLy tiến long</t>
+  </si>
+  <si>
+    <t>ĐL Anh Tuấn BG</t>
+  </si>
+  <si>
+    <t>ĐL SEA</t>
+  </si>
+  <si>
+    <t>Hải Yến</t>
+  </si>
+  <si>
+    <t>AT Việt Nam</t>
+  </si>
+  <si>
+    <t>Tiến Long</t>
+  </si>
+  <si>
+    <t>Anh Trực</t>
+  </si>
+  <si>
+    <t>Việt Bảo Tín</t>
+  </si>
+  <si>
+    <t>ĐL Minh Huy</t>
+  </si>
+  <si>
+    <t>Cao Anh Vương</t>
+  </si>
+  <si>
+    <t>ĐL Anh Trực</t>
+  </si>
+  <si>
+    <t>Anh Thái Quy Nhơn</t>
+  </si>
+  <si>
+    <t>Số Lượng Vỏ Cần Thay</t>
+  </si>
+  <si>
+    <t>Ngày Nhận Về</t>
+  </si>
+  <si>
+    <t>Tên Đại Lý</t>
+  </si>
+  <si>
+    <t>Danh sách xuất vỏ thiết bị TG102LE 2G nâng cấp 4G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A46TT19, Tổ dân phố 13, Phường Phúc La, Quận Hà Đông , Hà Nội </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công ty cổ phần công nghệ điện tử &amp; viễn thông Việt Nam  </t>
   </si>
 </sst>
 </file>
@@ -124,10 +189,17 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -220,8 +292,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,6 +324,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,142 +488,176 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="17" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{85E637A9-F304-4235-BA2E-9EF91B4075BD}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{9723A6C3-DC89-4D0E-A51B-99FD010154F3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -945,66 +1078,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="34" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="37" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="37" t="s">
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="39" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="40"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1111,40 +1244,40 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42" t="s">
+      <c r="B13" s="23"/>
+      <c r="C13" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42" t="s">
+      <c r="D13" s="23"/>
+      <c r="E13" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42" t="s">
+      <c r="F13" s="23"/>
+      <c r="G13" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="42"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41" t="s">
+      <c r="D14" s="22"/>
+      <c r="E14" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41" t="s">
+      <c r="F14" s="22"/>
+      <c r="G14" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="41"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
@@ -1197,22 +1330,22 @@
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42" t="s">
+      <c r="B20" s="23"/>
+      <c r="C20" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42" t="s">
+      <c r="D20" s="23"/>
+      <c r="E20" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42" t="s">
+      <c r="F20" s="23"/>
+      <c r="G20" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="42"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1238,27 +1371,564 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB78C2EE-39C3-4438-9FA1-A32E37E01FD3}">
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" style="44" customWidth="1"/>
+    <col min="2" max="2" width="30" style="45" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="45" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="43"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="45"/>
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="50">
+        <v>1</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="51">
+        <v>45922</v>
+      </c>
+      <c r="D7" s="50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="50">
+        <v>2</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="51">
+        <v>45930</v>
+      </c>
+      <c r="D8" s="50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="50">
+        <v>3</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="51">
+        <v>45932</v>
+      </c>
+      <c r="D9" s="50">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="50">
+        <v>4</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="51">
+        <v>45933</v>
+      </c>
+      <c r="D10" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="50">
+        <v>5</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="51">
+        <v>45934</v>
+      </c>
+      <c r="D11" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="50">
+        <v>6</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="51">
+        <v>45934</v>
+      </c>
+      <c r="D12" s="50">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="50">
+        <v>7</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="51">
+        <v>45938</v>
+      </c>
+      <c r="D13" s="50">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="50">
+        <v>8</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="51">
+        <v>45939</v>
+      </c>
+      <c r="D14" s="50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="50">
+        <v>9</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="51">
+        <v>45957</v>
+      </c>
+      <c r="D15" s="50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="50">
+        <v>10</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="51">
+        <v>45959</v>
+      </c>
+      <c r="D16" s="50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="50">
+        <v>11</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="51">
+        <v>45959</v>
+      </c>
+      <c r="D17" s="50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="50">
+        <v>12</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="51">
+        <v>45960</v>
+      </c>
+      <c r="D18" s="50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="50">
+        <v>13</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="51">
+        <v>45968</v>
+      </c>
+      <c r="D19" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="50">
+        <v>14</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="51">
+        <v>45975</v>
+      </c>
+      <c r="D20" s="50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="50">
+        <v>15</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="51">
+        <v>45982</v>
+      </c>
+      <c r="D21" s="50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="50">
+        <v>16</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="51">
+        <v>45982</v>
+      </c>
+      <c r="D22" s="50">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="50">
+        <v>17</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="51">
+        <v>45985</v>
+      </c>
+      <c r="D23" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="50">
+        <v>18</v>
+      </c>
+      <c r="B24" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="51">
+        <v>45986</v>
+      </c>
+      <c r="D24" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="50">
+        <v>19</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="51">
+        <v>45990</v>
+      </c>
+      <c r="D25" s="50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="50">
+        <v>20</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="51">
+        <v>45994</v>
+      </c>
+      <c r="D26" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="50">
+        <v>21</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="51">
+        <v>45996</v>
+      </c>
+      <c r="D27" s="50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="50">
+        <v>22</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="51">
+        <v>45999</v>
+      </c>
+      <c r="D28" s="50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="50">
+        <v>23</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="51">
+        <v>46007</v>
+      </c>
+      <c r="D29" s="50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="50">
+        <v>24</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="51">
+        <v>46008</v>
+      </c>
+      <c r="D30" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="50">
+        <v>25</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="51">
+        <v>46009</v>
+      </c>
+      <c r="D31" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="50">
+        <v>26</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="51">
+        <v>46013</v>
+      </c>
+      <c r="D32" s="50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="50">
+        <v>27</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="51">
+        <v>46014</v>
+      </c>
+      <c r="D33" s="50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="50">
+        <v>28</v>
+      </c>
+      <c r="B34" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="51">
+        <v>46028</v>
+      </c>
+      <c r="D34" s="50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="50">
+        <v>29</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="51">
+        <v>46032</v>
+      </c>
+      <c r="D35" s="50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="50">
+        <v>30</v>
+      </c>
+      <c r="B36" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="51">
+        <v>46048</v>
+      </c>
+      <c r="D36" s="50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="50">
+        <v>31</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="51">
+        <v>46050</v>
+      </c>
+      <c r="D37" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="50">
+        <v>32</v>
+      </c>
+      <c r="B38" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="51">
+        <v>46084</v>
+      </c>
+      <c r="D38" s="50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="50">
+        <v>33</v>
+      </c>
+      <c r="B39" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="51">
+        <v>46084</v>
+      </c>
+      <c r="D39" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="48"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="46">
+        <f>SUM(D7:D39)</f>
+        <v>350</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A40:C40"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>